--- a/Base/Backlog_40.xlsx
+++ b/Base/Backlog_40.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0D5F3D-8C2E-47F2-B8F2-4520FB0CCCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC050757-DE61-4276-A029-9CF8AD5BB5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>

--- a/Base/Backlog_40.xlsx
+++ b/Base/Backlog_40.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC050757-DE61-4276-A029-9CF8AD5BB5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27459DB-5BEB-4EA9-8BC3-F3757253819F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -115,9 +115,6 @@
     <t>SPN</t>
   </si>
   <si>
-    <t>Denis Silva</t>
-  </si>
-  <si>
     <t>Willian Rios</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Denis da Silva</t>
   </si>
 </sst>
 </file>
@@ -733,7 +733,7 @@
         <v>45936</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>14</v>
@@ -803,7 +803,7 @@
         <v>45936</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>14</v>
@@ -838,7 +838,7 @@
         <v>45936</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>14</v>
@@ -873,7 +873,7 @@
         <v>45936</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>14</v>
@@ -908,7 +908,7 @@
         <v>45936</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>14</v>
@@ -943,7 +943,7 @@
         <v>45936</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>14</v>
@@ -978,7 +978,7 @@
         <v>45936</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>14</v>
@@ -1013,7 +1013,7 @@
         <v>45936</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>14</v>
@@ -1048,7 +1048,7 @@
         <v>45936</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>14</v>
@@ -1083,7 +1083,7 @@
         <v>45936</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>14</v>
@@ -1153,7 +1153,7 @@
         <v>45936</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>14</v>
@@ -1223,7 +1223,7 @@
         <v>45936</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>14</v>
@@ -1258,7 +1258,7 @@
         <v>45936</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>14</v>
@@ -1328,7 +1328,7 @@
         <v>45936</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>14</v>
@@ -1468,7 +1468,7 @@
         <v>45936</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K24" s="15" t="s">
         <v>14</v>
@@ -1503,7 +1503,7 @@
         <v>45936</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K25" s="15" t="s">
         <v>14</v>
@@ -1538,7 +1538,7 @@
         <v>45936</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K26" s="15" t="s">
         <v>14</v>
@@ -1573,7 +1573,7 @@
         <v>45936</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K27" s="15" t="s">
         <v>14</v>
@@ -1608,7 +1608,7 @@
         <v>45936</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K28" s="15" t="s">
         <v>14</v>
@@ -1678,7 +1678,7 @@
         <v>45936</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>14</v>
@@ -1713,7 +1713,7 @@
         <v>45936</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K31" s="15" t="s">
         <v>14</v>
@@ -1748,7 +1748,7 @@
         <v>45936</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K32" s="15" t="s">
         <v>14</v>
@@ -1783,7 +1783,7 @@
         <v>45936</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K33" s="15" t="s">
         <v>14</v>
@@ -1888,7 +1888,7 @@
         <v>45936</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K36" s="15" t="s">
         <v>14</v>
@@ -2105,7 +2105,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
         <v>2025</v>
@@ -2129,10 +2129,10 @@
         <v>45936</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2140,7 +2140,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3">
         <v>2025</v>
@@ -2167,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2175,7 +2175,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3">
         <v>2025</v>
@@ -2199,10 +2199,10 @@
         <v>45936</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2210,7 +2210,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3">
         <v>2025</v>
@@ -2237,7 +2237,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2245,7 +2245,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3">
         <v>2025</v>
@@ -2269,10 +2269,10 @@
         <v>45936</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2280,7 +2280,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3">
         <v>2025</v>
@@ -2307,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2315,7 +2315,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3">
         <v>2025</v>
@@ -2342,7 +2342,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
